--- a/NBFC-MF/Borrowers/Ashalata_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Ashalata_Weekly.xlsx
@@ -827,31 +827,33 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="22" t="str">
+      <c r="A4" s="2">
+        <v>46290</v>
+      </c>
+      <c r="B4" s="22">
         <f t="shared" ref="B4:B18" si="3">IF(A4&lt;&gt;"",B3+1,"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="C4" s="3"/>
-      <c r="D4" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E4" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F4" s="1" t="str">
+      <c r="D4" s="1">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="E4" s="1">
+        <f t="shared" si="1"/>
+        <v>90.141955730996514</v>
+      </c>
+      <c r="F4" s="1">
         <f t="shared" ref="F4:F18" si="4">IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),D4-E4,"")</f>
-        <v/>
-      </c>
-      <c r="G4" s="1" t="str">
+        <v>259.85804426900347</v>
+      </c>
+      <c r="G4" s="1">
         <f t="shared" ref="G4:G18" si="5">IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),G3-F4,"")</f>
-        <v/>
-      </c>
-      <c r="H4" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>4235.6498555067847</v>
+      </c>
+      <c r="H4" s="1">
+        <f t="shared" si="2"/>
+        <v>764.35014449321534</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>11</v>
@@ -1120,7 +1122,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1155,7 +1157,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>5250</v>
+        <v>4900</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1190,7 +1192,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>4495.5078997757882</v>
+        <v>4235.6498555067847</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1225,7 +1227,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>504.49210022421175</v>
+        <v>764.35014449321534</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Ashalata_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Ashalata_Weekly.xlsx
@@ -861,31 +861,33 @@
       <c r="K4" s="26"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="19"/>
-      <c r="B5" s="23" t="str">
+      <c r="A5" s="19">
+        <v>46297</v>
+      </c>
+      <c r="B5" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>4</v>
       </c>
       <c r="C5" s="20"/>
-      <c r="D5" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E5" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F5" s="21" t="str">
+      <c r="D5" s="21">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="E5" s="21">
+        <f t="shared" si="1"/>
+        <v>84.931396024493026</v>
+      </c>
+      <c r="F5" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G5" s="21" t="str">
+        <v>265.06860397550696</v>
+      </c>
+      <c r="G5" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H5" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>3970.5812515312778</v>
+      </c>
+      <c r="H5" s="21">
+        <f t="shared" si="2"/>
+        <v>1029.4187484687222</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>12</v>
@@ -893,31 +895,33 @@
       <c r="K5" s="26"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="22" t="str">
+      <c r="A6" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B6" s="22">
         <f t="shared" si="3"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E6" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F6" s="1" t="str">
+      <c r="D6" s="1">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="E6" s="1">
+        <f t="shared" si="1"/>
+        <v>79.616356456565924</v>
+      </c>
+      <c r="F6" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G6" s="1" t="str">
+        <v>270.38364354343406</v>
+      </c>
+      <c r="G6" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H6" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>3700.1976079878436</v>
+      </c>
+      <c r="H6" s="1">
+        <f t="shared" si="2"/>
+        <v>1299.8023920121564</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>13</v>
@@ -1122,7 +1126,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1157,7 +1161,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>4900</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1192,7 +1196,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>4235.6498555067847</v>
+        <v>3700.1976079878436</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1227,7 +1231,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>764.35014449321534</v>
+        <v>1299.8023920121564</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
